--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -503,7 +503,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -518,7 +518,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -548,7 +548,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -563,7 +563,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -578,7 +578,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -593,7 +593,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -608,7 +608,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -623,7 +623,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -638,7 +638,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -668,7 +668,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -683,7 +683,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -698,7 +698,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -713,7 +713,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -725,6 +725,21 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -503,7 +503,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -518,7 +518,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -548,7 +548,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -563,7 +563,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -578,7 +578,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -593,7 +593,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -608,7 +608,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -623,7 +623,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -638,7 +638,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -668,7 +668,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -683,7 +683,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -698,7 +698,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -713,7 +713,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -725,6 +725,21 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>6ZfxDZ5t</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -503,7 +503,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -515,231 +515,6 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>IgtCPCkn</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tYQyK8JN</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>6FCg7VZH</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>bk9o9i55</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>vmgpBDzg</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>CKcVGr7E</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>pSpI7vU0</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ppvl45N8</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,44 +436,74 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_val_player_sub</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -484,11 +514,17 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -499,11 +535,17 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -514,6 +556,243 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -566,7 +566,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -689,111 +689,6 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -566,7 +566,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -566,7 +566,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -668,27 +668,6 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>vmgpBDzg</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -566,7 +566,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -605,69 +605,6 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tYQyK8JN</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>6FCg7VZH</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>bk9o9i55</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>6ZfxDZ5t</t>
+          <t>Qw81zU34</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>E3tkRPQj</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>fJaIWo3T</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -566,28 +566,42 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>-0.4608407587807674</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4023131698713805</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.02923278201333535</v>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0.2601887464124737</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>-0.2050051643443854</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1001822662169108</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -605,6 +619,104 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>8MPiooIM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>CGH7Enso</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0dMqm7mA</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>-0.4608407587807674</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4023131698713805</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02923278201333535</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>0.2601887464124737</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>-0.2050051643443854</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.1001822662169108</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>vsYzkTIc</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,74 +436,29 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>dif_mean_age_player_start</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_pot_player_sub</t>
+          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_val_player_sub</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
           <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>S66OuPup</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -511,20 +466,11 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>EsTauGo1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -532,20 +478,11 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>nTCJapXF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -553,55 +490,23 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>-0.4608407587807674</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.4023131698713805</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.02923278201333535</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>0.2601887464124737</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>-0.2050051643443854</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.1001822662169108</v>
-      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -609,41 +514,29 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8MPiooIM</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.03591618173566233</v>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.2587164934235492</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CGH7Enso</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -651,55 +544,23 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0dMqm7mA</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>-0.4608407587807674</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.4023131698713805</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.02923278201333535</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>0.2601887464124737</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>-0.2050051643443854</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.1001822662169108</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vsYzkTIc</t>
+          <t>0K4Ww3Ad</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -707,15 +568,120 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.03591618173566233</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0.2587164934235492</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>hCffxjZi</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8MPiooIM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>CGH7Enso</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>0dMqm7mA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>vsYzkTIc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>S66OuPup</t>
+          <t>Qw81zU34</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -470,7 +470,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EsTauGo1</t>
+          <t>E3tkRPQj</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -482,7 +482,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nTCJapXF</t>
+          <t>fJaIWo3T</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -494,19 +494,25 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6HPisxHl</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.8245676452155679</v>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.2848372292752816</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6V4QeyWs</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -515,174 +521,6 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>v39B1623</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.03591618173566233</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>0.2587164934235492</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>noOg1c8K</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>fiy8wfGD</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>0K4Ww3Ad</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Qw81zU34</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>fJaIWo3T</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>E3tkRPQj</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.03591618173566233</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>0.2587164934235492</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>hCffxjZi</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8MPiooIM</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>CGH7Enso</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>0dMqm7mA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>vsYzkTIc</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -470,7 +470,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -482,37 +482,37 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.1531740127245793</v>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.0866412295641513</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.8245676452155679</v>
-      </c>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>0.2848372292752816</v>
-      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>lxyu7Met</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -521,6 +521,168 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.1531740127245793</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.0866412295641513</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
+          <t>S66OuPup</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -470,7 +470,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
+          <t>EsTauGo1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -482,25 +482,19 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.1531740127245793</v>
-      </c>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>0.0866412295641513</v>
-      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
+          <t>nTCJapXF</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -512,7 +506,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>lxyu7Met</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -524,19 +518,25 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>xb7MlutC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6406915741999656</v>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.3661046787403449</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v3PZcqJP</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -548,7 +548,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zBdshgV6</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -557,132 +557,6 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>S66OuPup</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>6HPisxHl</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>EsTauGo1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>nTCJapXF</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6V4QeyWs</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>v39B1623</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.1531740127245793</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="n">
-        <v>0.0866412295641513</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>noOg1c8K</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>fiy8wfGD</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>0K4Ww3Ad</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,16 +441,6 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
@@ -458,68 +448,182 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>rZUMHwAb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>4nvCemgd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.8245676452155679</v>
-      </c>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>0.2848372292752816</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>IHSe3ve5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Wf14adfU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>z9REJaun</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xYNVFHvB</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -458,7 +458,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>p4Um50Qh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -468,7 +468,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -478,7 +478,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>bDeVnJAO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -488,7 +488,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>lxyu7Met</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -498,7 +498,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>xb7MlutC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -508,7 +508,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>v3PZcqJP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -518,7 +518,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>zBdshgV6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -528,102 +528,12 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>MRfkjXaJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>xb7MlutC</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>v3PZcqJP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>zBdshgV6</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,56 +485,6 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>xb7MlutC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>v3PZcqJP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zBdshgV6</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_start</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -448,42 +463,236 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.4770873468466314</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4219816391860958</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.07668886763718745</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.05634448291646473</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2929448414309503</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.4770873468466314</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4219816391860958</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.07668886763718745</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05634448291646473</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2929448414309503</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4770873468466314</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4219816391860958</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07668886763718745</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05634448291646473</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2929448414309503</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4770873468466314</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4219816391860958</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.07668886763718745</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.05634448291646473</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2929448414309503</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.4770873468466314</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4219816391860958</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.05634448291646473</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2929448414309503</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.4770873468466314</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4219816391860958</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.07668886763718745</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05634448291646473</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2929448414309503</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.4770873468466314</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4219816391860958</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07668886763718745</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.05634448291646473</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2929448414309503</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Wf14adfU</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.4770873468466314</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4219816391860958</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0.05634448291646473</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2929448414309503</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>z9REJaun</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xYNVFHvB</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.4770873468466314</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4219816391860958</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.07668886763718745</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.05634448291646473</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.2929448414309503</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,236 +463,316 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4770873468466314</v>
+        <v>-0.07007846772542183</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4219816391860958</v>
+        <v>-1.216149413127242</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07668886763718745</v>
+        <v>-0.007024646658704578</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05634448291646473</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.2929448414309503</v>
-      </c>
+        <v>-0.1261814546045382</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4770873468466314</v>
+        <v>-0.07007846772542183</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4219816391860958</v>
+        <v>-1.216149413127242</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07668886763718745</v>
+        <v>-0.007024646658704578</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05634448291646473</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.2929448414309503</v>
-      </c>
+        <v>-0.1261814546045382</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.4770873468466314</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.4219816391860958</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.07668886763718745</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.05634448291646473</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.2929448414309503</v>
-      </c>
+        <v>-0.007024646658704578</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4770873468466314</v>
+        <v>-0.07007846772542183</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4219816391860958</v>
+        <v>-1.216149413127242</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07668886763718745</v>
+        <v>-0.007024646658704578</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05634448291646473</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.2929448414309503</v>
-      </c>
+        <v>-0.1261814546045382</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4770873468466314</v>
+        <v>-0.07007846772542183</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4219816391860958</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>-1.216149413127242</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.007024646658704578</v>
+      </c>
       <c r="F6" t="n">
-        <v>0.05634448291646473</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.2929448414309503</v>
-      </c>
+        <v>-0.1261814546045382</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4770873468466314</v>
+        <v>-0.07007846772542183</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4219816391860958</v>
+        <v>-1.216149413127242</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07668886763718745</v>
+        <v>-0.007024646658704578</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05634448291646473</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.2929448414309503</v>
-      </c>
+        <v>-0.1261814546045382</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4770873468466314</v>
+        <v>-0.07007846772542183</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4219816391860958</v>
+        <v>-1.216149413127242</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07668886763718745</v>
+        <v>-0.007024646658704578</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05634448291646473</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.2929448414309503</v>
-      </c>
+        <v>-0.1261814546045382</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4770873468466314</v>
+        <v>-0.07007846772542183</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4219816391860958</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>-1.216149413127242</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.007024646658704578</v>
+      </c>
       <c r="F9" t="n">
-        <v>0.05634448291646473</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.2929448414309503</v>
-      </c>
+        <v>-0.1261814546045382</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.07007846772542183</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.216149413127242</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.007024646658704578</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.1261814546045382</v>
+      </c>
       <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4770873468466314</v>
+        <v>-0.07007846772542183</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4219816391860958</v>
+        <v>-1.216149413127242</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07668886763718745</v>
+        <v>-0.007024646658704578</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05634448291646473</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.2929448414309503</v>
-      </c>
+        <v>-0.1261814546045382</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.07007846772542183</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.216149413127242</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.007024646658704578</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.1261814546045382</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.07007846772542183</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.216149413127242</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.007024646658704578</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.1261814546045382</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.07007846772542183</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.216149413127242</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>-0.1261814546045382</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.07007846772542183</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.216149413127242</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.007024646658704578</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.1261814546045382</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,20 +441,45 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -463,316 +488,594 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>AsQgyP6l</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.07007846772542183</v>
+        <v>-0.279348596452377</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.216149413127242</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-0.1261814546045382</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>KdJMr7EE</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.07007846772542183</v>
+        <v>-0.279348596452377</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.216149413127242</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.1261814546045382</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>vNHAXt6D</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
+      <c r="C4" t="n">
+        <v>-0.279348596452377</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
+          <t>h2acepbK</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.07007846772542183</v>
+        <v>-0.279348596452377</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.216149413127242</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.1261814546045382</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>WdE2Z2y1</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.07007846772542183</v>
+        <v>-0.279348596452377</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.216149413127242</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.1261814546045382</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>S2WzL3M7</t>
+          <t>vaZNtoqR</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.07007846772542183</v>
+        <v>-0.279348596452377</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.216149413127242</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.1261814546045382</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OAZJOoNr</t>
+          <t>hQspntL6</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.07007846772542183</v>
+        <v>-0.279348596452377</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.216149413127242</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0.1261814546045382</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WzwSMPie</t>
+          <t>p0vxl2jf</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="n">
-        <v>-0.07007846772542183</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-1.216149413127242</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-0.1261814546045382</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.07007846772542183</v>
+        <v>-0.279348596452377</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.216149413127242</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-0.1261814546045382</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.07007846772542183</v>
+        <v>-0.279348596452377</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.216149413127242</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.1261814546045382</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C12" t="n">
-        <v>-0.07007846772542183</v>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>-1.216149413127242</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.1261814546045382</v>
-      </c>
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.07007846772542183</v>
+        <v>-0.279348596452377</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.216149413127242</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-0.1261814546045382</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.07007846772542183</v>
+        <v>-0.279348596452377</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.216149413127242</v>
+        <v>-0.05056661293584868</v>
       </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>-0.1261814546045382</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.07007846772542183</v>
+        <v>-0.279348596452377</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.216149413127242</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.007024646658704578</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.1261814546045382</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>S2WzL3M7</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.279348596452377</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OAZJOoNr</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.279348596452377</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>WzwSMPie</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.279348596452377</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.279348596452377</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.05056661293584868</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>-0.8270585621767588</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>-0.08866144095890205</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.3054759171730904</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.01132326390554637</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.5162609149027396</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,35 +451,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_wage_player_sub</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_pot_player_sub</t>
+          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_sum_value_player_miss</t>
+          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_value_player_sub</t>
+          <t>dif_mean_rep_player_start</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -491,135 +481,67 @@
           <t>AsQgyP6l</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>vNHAXt6D</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>-0.06735832146285205</v>
+      </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -630,30 +552,16 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>-0.06735832146285205</v>
+      </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -661,33 +569,15 @@
           <t>vaZNtoqR</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -695,33 +585,15 @@
           <t>hQspntL6</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -729,9 +601,7 @@
           <t>p0vxl2jf</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -740,8 +610,6 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -749,33 +617,15 @@
           <t>lYpTkOLs</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -783,61 +633,35 @@
           <t>nVutWTU8</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>-0.06735832146285205</v>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -845,67 +669,31 @@
           <t>WMcg8Qx2</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -916,30 +704,16 @@
       <c r="B15" t="n">
         <v>1</v>
       </c>
-      <c r="C15" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>-0.06735832146285205</v>
+      </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -947,33 +721,15 @@
           <t>S2WzL3M7</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -981,33 +737,15 @@
           <t>OAZJOoNr</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1015,33 +753,15 @@
           <t>WzwSMPie</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1049,33 +769,15 @@
           <t>vwbmU7aL</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.279348596452377</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-0.05056661293584868</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="n">
-        <v>-0.8270585621767588</v>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>-0.08866144095890205</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-0.3054759171730904</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-0.01132326390554637</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-0.5162609149027396</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AsQgyP6l</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -494,7 +494,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -503,7 +503,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>-0.06735832146285205</v>
+        <v>-0.4429167405696857</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -514,7 +514,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -530,7 +530,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -546,7 +546,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WdE2Z2y1</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -555,7 +555,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>-0.06735832146285205</v>
+        <v>-0.4429167405696857</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -563,222 +563,6 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>vaZNtoqR</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>hQspntL6</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>p0vxl2jf</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>lYpTkOLs</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>nVutWTU8</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>-0.06735832146285205</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>WMcg8Qx2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>h8K6HUFF</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>b9aoAn8k</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="n">
-        <v>-0.06735832146285205</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>S2WzL3M7</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OAZJOoNr</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>WzwSMPie</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>vwbmU7aL</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>UTsToXQN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -494,17 +494,13 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>-0.4429167405696857</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -514,14 +510,18 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>-0.1151439471196815</v>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -530,13 +530,17 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>-0.0500208688277356</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -546,23 +550,249 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>-0.4429167405696857</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>-0.0500208688277356</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>-0.1151439471196815</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>-0.0500208688277356</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WdE2Z2y1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>-0.0500208688277356</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.1151439471196815</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vaZNtoqR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>hQspntL6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p0vxl2jf</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>-0.1151439471196815</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>lYpTkOLs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UTsToXQN</t>
+          <t>AsQgyP6l</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -494,7 +494,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Y1lKmgdB</t>
+          <t>h2acepbK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -510,7 +510,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EuWhpKkJ</t>
+          <t>vNHAXt6D</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -518,10 +518,10 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>-0.1151439471196815</v>
-      </c>
+      <c r="E4" t="n">
+        <v>-0.164345262647561</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -530,17 +530,13 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4Md3iycn</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>-0.0500208688277356</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -550,14 +546,20 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vuBo4Eth</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>WdE2Z2y1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>-0.164345262647561</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.2185916537127182</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -566,7 +568,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>n5Eg2hB4</t>
+          <t>vaZNtoqR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -582,7 +584,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rX720WuH</t>
+          <t>hQspntL6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -598,7 +600,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bqYbtBlo</t>
+          <t>p0vxl2jf</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -606,10 +608,10 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="n">
-        <v>-0.0500208688277356</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>-0.2185916537127182</v>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -618,181 +620,19 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0ljCkFRb</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
+          <t>lYpTkOLs</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
-        <v>-0.1151439471196815</v>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>AsQgyP6l</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>h2acepbK</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>KdJMr7EE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vNHAXt6D</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="n">
-        <v>-0.0500208688277356</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WdE2Z2y1</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="n">
-        <v>-0.0500208688277356</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.1151439471196815</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>vaZNtoqR</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>hQspntL6</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>p0vxl2jf</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="n">
-        <v>-0.1151439471196815</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>lYpTkOLs</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,13 +478,17 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AsQgyP6l</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>b59ZhlYj</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>-0.1224543289975021</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -494,7 +498,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -510,7 +514,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -519,7 +523,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>-0.164345262647561</v>
+        <v>-0.1224543289975021</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -530,7 +534,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -546,20 +550,14 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WdE2Z2y1</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
+          <t>l8H0Dwy3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>-0.164345262647561</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.2185916537127182</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -568,14 +566,18 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vaZNtoqR</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>dYK8BH5F</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.143561564087779</v>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -584,7 +586,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hQspntL6</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -600,18 +602,14 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>p0vxl2jf</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+          <t>figxD9PM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>-0.2185916537127182</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -620,19 +618,183 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>lYpTkOLs</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>Gp6AbAAT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0.143561564087779</v>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0.143561564087779</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>-0.1224543289975021</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>-0.1224543289975021</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0.143561564087779</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,17 +478,13 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>b59ZhlYj</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>-0.1224543289975021</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -498,14 +494,18 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nRkUEVfA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>-0.003106648346881791</v>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -514,17 +514,13 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WWnG5RHd</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>-0.1224543289975021</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -534,13 +530,17 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QB1LGiQc</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>0.06467047451419272</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -550,7 +550,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>l8H0Dwy3</t>
+          <t>vuBo4Eth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -566,18 +566,14 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dYK8BH5F</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>0.143561564087779</v>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -586,7 +582,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bJl87mmp</t>
+          <t>rX720WuH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -602,13 +598,17 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>figxD9PM</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>0.06467047451419272</v>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -618,7 +618,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gp6AbAAT</t>
+          <t>0ljCkFRb</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -628,173 +628,13 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.143561564087779</v>
+        <v>-0.003106648346881791</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>UTsToXQN</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Y1lKmgdB</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>EuWhpKkJ</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="n">
-        <v>0.143561564087779</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>4Md3iycn</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="n">
-        <v>-0.1224543289975021</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>vuBo4Eth</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>n5Eg2hB4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>rX720WuH</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>bqYbtBlo</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>-0.1224543289975021</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>0ljCkFRb</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0.143561564087779</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,35 +441,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_value_player_start</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_wage_player_start</t>
+          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -478,7 +458,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UTsToXQN</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -486,35 +466,23 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EuWhpKkJ</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
+          <t>nRkUEVfA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>-0.003106648346881791</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Y1lKmgdB</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -522,35 +490,23 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4Md3iycn</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
+          <t>WWnG5RHd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>0.06467047451419272</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vuBo4Eth</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -558,15 +514,11 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>n5Eg2hB4</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -574,15 +526,11 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rX720WuH</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -590,50 +538,30 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bqYbtBlo</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+          <t>figxD9PM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="n">
-        <v>0.06467047451419272</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0ljCkFRb</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
+          <t>Gp6AbAAT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
-        <v>-0.003106648346881791</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,132 +436,168 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_pot_player_sub</t>
+          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>b59ZhlYj</t>
+          <t>GryrQGK8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nRkUEVfA</t>
+          <t>SMfm4Zck</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QB1LGiQc</t>
+          <t>Im9H9ezS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WWnG5RHd</t>
+          <t>xdpX3Q36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>l8H0Dwy3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>b59ZhlYj</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1388559338176552</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.08196614663475578</v>
+      </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dYK8BH5F</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bJl87mmp</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>figxD9PM</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gp6AbAAT</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dYK8BH5F</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>bJl87mmp</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>figxD9PM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Gp6AbAAT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
